--- a/data/usuarios_sistema_completo.xlsx
+++ b/data/usuarios_sistema_completo.xlsx
@@ -5721,7 +5721,7 @@
     <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="51.86214285714286" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
